--- a/artfynd/A 37208-2026 artfynd.xlsx
+++ b/artfynd/A 37208-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480989</v>
       </c>
       <c r="B2" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480976</v>
       </c>
       <c r="B3" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136480944</v>
       </c>
       <c r="B4" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37208-2026 artfynd.xlsx
+++ b/artfynd/A 37208-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480989</v>
       </c>
       <c r="B2" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480976</v>
       </c>
       <c r="B3" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136480944</v>
       </c>
       <c r="B4" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37208-2026 artfynd.xlsx
+++ b/artfynd/A 37208-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480989</v>
       </c>
       <c r="B2" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480976</v>
       </c>
       <c r="B3" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136480944</v>
       </c>
       <c r="B4" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37208-2026 artfynd.xlsx
+++ b/artfynd/A 37208-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480989</v>
       </c>
       <c r="B2" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480976</v>
       </c>
       <c r="B3" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136480944</v>
       </c>
       <c r="B4" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37208-2026 artfynd.xlsx
+++ b/artfynd/A 37208-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480989</v>
       </c>
       <c r="B2" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136480976</v>
       </c>
       <c r="B3" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136480944</v>
       </c>
       <c r="B4" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
